--- a/templates/ERC000035/metadata_template_ERC000035.xlsx
+++ b/templates/ERC000035/metadata_template_ERC000035.xlsx
@@ -24,7 +24,7 @@
     <definedName name="experimentalfactor5">'cv_sample'!$AG$1:$AG$35</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="geographiclocationcountryandorsea">'cv_sample'!$O$1:$O$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$85</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="812" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="637">
   <si>
     <t>alias</t>
   </si>
@@ -560,6 +560,9 @@
     <t>DNBSEQ-G50</t>
   </si>
   <si>
+    <t>DNBSEQ-G800</t>
+  </si>
+  <si>
     <t>DNBSEQ-T10x4RS</t>
   </si>
   <si>
@@ -723,6 +726,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>Vega</t>
   </si>
   <si>
     <t>instrument_model</t>
@@ -2470,7 +2476,7 @@
         <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2514,7 +2520,7 @@
         <v>144</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2541,7 +2547,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N85"/>
+  <dimension ref="G1:N87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3260,6 +3266,16 @@
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="86" spans="14:14">
+      <c r="N86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3281,27 +3297,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3321,122 +3337,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3460,240 +3476,240 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AI1" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="AM1" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="AJ1" s="1" t="s">
-        <v>629</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>609</v>
-      </c>
       <c r="AN1" s="1" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="2" spans="1:40" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
   </sheetData>
@@ -3728,1972 +3744,1972 @@
   <sheetData>
     <row r="1" spans="15:33">
       <c r="O1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AC1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AD1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AE1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AF1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AG1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="2" spans="15:33">
       <c r="O2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AC2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AD2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AE2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AF2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AG2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="15:33">
       <c r="O3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AC3" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AD3" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AE3" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AF3" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AG3" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="4" spans="15:33">
       <c r="O4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AC4" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AD4" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AE4" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AF4" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AG4" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="5" spans="15:33">
       <c r="O5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AC5" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AD5" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AE5" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AF5" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AG5" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="6" spans="15:33">
       <c r="O6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AC6" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AD6" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AE6" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AF6" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AG6" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="7" spans="15:33">
       <c r="O7" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AC7" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AD7" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AE7" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AF7" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AG7" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8" spans="15:33">
       <c r="O8" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AC8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AD8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AE8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AF8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="15:33">
       <c r="O9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AC9" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AD9" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AE9" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AF9" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AG9" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="10" spans="15:33">
       <c r="O10" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AC10" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AD10" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AE10" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AF10" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AG10" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="11" spans="15:33">
       <c r="O11" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AC11" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AD11" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AE11" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AF11" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="AG11" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="12" spans="15:33">
       <c r="O12" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AC12" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AD12" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AE12" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AF12" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AG12" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="13" spans="15:33">
       <c r="O13" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AC13" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AD13" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AE13" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AF13" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AG13" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="14" spans="15:33">
       <c r="O14" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AC14" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AD14" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AE14" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AF14" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="AG14" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="15" spans="15:33">
       <c r="O15" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AC15" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AD15" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AE15" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AF15" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="AG15" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="16" spans="15:33">
       <c r="O16" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AC16" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AD16" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AE16" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AF16" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AG16" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="17" spans="15:33">
       <c r="O17" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AC17" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AD17" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AE17" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AF17" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AG17" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="18" spans="15:33">
       <c r="O18" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AC18" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AD18" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AE18" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AF18" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG18" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="15:33">
       <c r="O19" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AC19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AD19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AE19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AF19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="15:33">
       <c r="O20" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AC20" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AD20" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AE20" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AF20" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AG20" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="21" spans="15:33">
       <c r="O21" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AC21" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AD21" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AE21" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AF21" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AG21" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="22" spans="15:33">
       <c r="O22" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AC22" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AD22" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AE22" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AF22" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AG22" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="23" spans="15:33">
       <c r="O23" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AC23" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AD23" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AE23" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AF23" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG23" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="24" spans="15:33">
       <c r="O24" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AC24" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AD24" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AE24" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AF24" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AG24" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="25" spans="15:33">
       <c r="O25" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AC25" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AD25" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AE25" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AF25" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AG25" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="26" spans="15:33">
       <c r="O26" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AC26" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AD26" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AE26" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AF26" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AG26" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="27" spans="15:33">
       <c r="O27" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AC27" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AD27" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AE27" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AF27" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AG27" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="28" spans="15:33">
       <c r="O28" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AC28" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AD28" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AE28" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AF28" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AG28" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="29" spans="15:33">
       <c r="O29" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AC29" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AD29" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AE29" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AF29" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AG29" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="30" spans="15:33">
       <c r="O30" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AC30" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AD30" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AE30" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AF30" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG30" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="31" spans="15:33">
       <c r="O31" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AC31" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AD31" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AE31" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AF31" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AG31" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="32" spans="15:33">
       <c r="O32" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AC32" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AD32" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AE32" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AF32" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AG32" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="33" spans="15:33">
       <c r="O33" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AC33" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AD33" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AE33" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AF33" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AG33" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
     </row>
     <row r="34" spans="15:33">
       <c r="O34" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AC34" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AD34" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AE34" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AF34" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AG34" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="35" spans="15:33">
       <c r="O35" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AC35" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AD35" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AE35" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AF35" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AG35" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="36" spans="15:33">
       <c r="O36" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="37" spans="15:33">
       <c r="O37" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="38" spans="15:33">
       <c r="O38" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="39" spans="15:33">
       <c r="O39" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="40" spans="15:33">
       <c r="O40" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="41" spans="15:33">
       <c r="O41" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="42" spans="15:33">
       <c r="O42" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="43" spans="15:33">
       <c r="O43" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="44" spans="15:33">
       <c r="O44" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="45" spans="15:33">
       <c r="O45" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="46" spans="15:33">
       <c r="O46" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="47" spans="15:33">
       <c r="O47" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="48" spans="15:33">
       <c r="O48" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="49" spans="15:15">
       <c r="O49" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="50" spans="15:15">
       <c r="O50" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="51" spans="15:15">
       <c r="O51" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="52" spans="15:15">
       <c r="O52" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="53" spans="15:15">
       <c r="O53" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="54" spans="15:15">
       <c r="O54" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="55" spans="15:15">
       <c r="O55" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="56" spans="15:15">
       <c r="O56" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="57" spans="15:15">
       <c r="O57" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="58" spans="15:15">
       <c r="O58" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="59" spans="15:15">
       <c r="O59" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="60" spans="15:15">
       <c r="O60" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="61" spans="15:15">
       <c r="O61" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="62" spans="15:15">
       <c r="O62" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="63" spans="15:15">
       <c r="O63" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="64" spans="15:15">
       <c r="O64" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="65" spans="15:15">
       <c r="O65" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="66" spans="15:15">
       <c r="O66" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="67" spans="15:15">
       <c r="O67" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="68" spans="15:15">
       <c r="O68" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="69" spans="15:15">
       <c r="O69" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="70" spans="15:15">
       <c r="O70" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="71" spans="15:15">
       <c r="O71" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="72" spans="15:15">
       <c r="O72" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="73" spans="15:15">
       <c r="O73" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="74" spans="15:15">
       <c r="O74" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="75" spans="15:15">
       <c r="O75" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="76" spans="15:15">
       <c r="O76" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="77" spans="15:15">
       <c r="O77" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="78" spans="15:15">
       <c r="O78" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="79" spans="15:15">
       <c r="O79" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="80" spans="15:15">
       <c r="O80" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="81" spans="15:15">
       <c r="O81" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="82" spans="15:15">
       <c r="O82" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="83" spans="15:15">
       <c r="O83" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="84" spans="15:15">
       <c r="O84" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="85" spans="15:15">
       <c r="O85" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="86" spans="15:15">
       <c r="O86" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="87" spans="15:15">
       <c r="O87" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="88" spans="15:15">
       <c r="O88" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="89" spans="15:15">
       <c r="O89" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="90" spans="15:15">
       <c r="O90" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="91" spans="15:15">
       <c r="O91" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="92" spans="15:15">
       <c r="O92" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="93" spans="15:15">
       <c r="O93" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="94" spans="15:15">
       <c r="O94" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="95" spans="15:15">
       <c r="O95" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="96" spans="15:15">
       <c r="O96" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="97" spans="15:15">
       <c r="O97" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="98" spans="15:15">
       <c r="O98" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="99" spans="15:15">
       <c r="O99" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="100" spans="15:15">
       <c r="O100" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="101" spans="15:15">
       <c r="O101" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="102" spans="15:15">
       <c r="O102" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="103" spans="15:15">
       <c r="O103" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="104" spans="15:15">
       <c r="O104" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="105" spans="15:15">
       <c r="O105" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="106" spans="15:15">
       <c r="O106" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="107" spans="15:15">
       <c r="O107" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="108" spans="15:15">
       <c r="O108" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="109" spans="15:15">
       <c r="O109" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="110" spans="15:15">
       <c r="O110" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="111" spans="15:15">
       <c r="O111" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="112" spans="15:15">
       <c r="O112" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="113" spans="15:15">
       <c r="O113" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="114" spans="15:15">
       <c r="O114" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="115" spans="15:15">
       <c r="O115" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="116" spans="15:15">
       <c r="O116" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="117" spans="15:15">
       <c r="O117" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="118" spans="15:15">
       <c r="O118" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="119" spans="15:15">
       <c r="O119" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="120" spans="15:15">
       <c r="O120" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="121" spans="15:15">
       <c r="O121" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="122" spans="15:15">
       <c r="O122" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="123" spans="15:15">
       <c r="O123" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="124" spans="15:15">
       <c r="O124" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="125" spans="15:15">
       <c r="O125" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="126" spans="15:15">
       <c r="O126" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="127" spans="15:15">
       <c r="O127" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="128" spans="15:15">
       <c r="O128" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="129" spans="15:15">
       <c r="O129" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="130" spans="15:15">
       <c r="O130" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="131" spans="15:15">
       <c r="O131" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="132" spans="15:15">
       <c r="O132" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="133" spans="15:15">
       <c r="O133" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="134" spans="15:15">
       <c r="O134" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="135" spans="15:15">
       <c r="O135" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="136" spans="15:15">
       <c r="O136" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="137" spans="15:15">
       <c r="O137" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="138" spans="15:15">
       <c r="O138" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="139" spans="15:15">
       <c r="O139" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="140" spans="15:15">
       <c r="O140" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="141" spans="15:15">
       <c r="O141" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="142" spans="15:15">
       <c r="O142" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="143" spans="15:15">
       <c r="O143" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="144" spans="15:15">
       <c r="O144" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="145" spans="15:15">
       <c r="O145" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="146" spans="15:15">
       <c r="O146" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="147" spans="15:15">
       <c r="O147" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="148" spans="15:15">
       <c r="O148" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="149" spans="15:15">
       <c r="O149" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="150" spans="15:15">
       <c r="O150" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="151" spans="15:15">
       <c r="O151" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="152" spans="15:15">
       <c r="O152" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="153" spans="15:15">
       <c r="O153" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="154" spans="15:15">
       <c r="O154" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="155" spans="15:15">
       <c r="O155" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="156" spans="15:15">
       <c r="O156" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="157" spans="15:15">
       <c r="O157" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="158" spans="15:15">
       <c r="O158" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="159" spans="15:15">
       <c r="O159" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="160" spans="15:15">
       <c r="O160" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="161" spans="15:15">
       <c r="O161" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="162" spans="15:15">
       <c r="O162" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="163" spans="15:15">
       <c r="O163" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="164" spans="15:15">
       <c r="O164" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="165" spans="15:15">
       <c r="O165" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="166" spans="15:15">
       <c r="O166" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="167" spans="15:15">
       <c r="O167" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="168" spans="15:15">
       <c r="O168" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="169" spans="15:15">
       <c r="O169" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="170" spans="15:15">
       <c r="O170" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="171" spans="15:15">
       <c r="O171" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="172" spans="15:15">
       <c r="O172" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="173" spans="15:15">
       <c r="O173" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="174" spans="15:15">
       <c r="O174" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="175" spans="15:15">
       <c r="O175" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="176" spans="15:15">
       <c r="O176" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="177" spans="15:15">
       <c r="O177" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="178" spans="15:15">
       <c r="O178" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="179" spans="15:15">
       <c r="O179" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="180" spans="15:15">
       <c r="O180" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="181" spans="15:15">
       <c r="O181" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="182" spans="15:15">
       <c r="O182" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="183" spans="15:15">
       <c r="O183" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="184" spans="15:15">
       <c r="O184" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="185" spans="15:15">
       <c r="O185" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="186" spans="15:15">
       <c r="O186" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="187" spans="15:15">
       <c r="O187" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="188" spans="15:15">
       <c r="O188" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="189" spans="15:15">
       <c r="O189" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="190" spans="15:15">
       <c r="O190" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="191" spans="15:15">
       <c r="O191" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="192" spans="15:15">
       <c r="O192" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="193" spans="15:15">
       <c r="O193" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="194" spans="15:15">
       <c r="O194" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="195" spans="15:15">
       <c r="O195" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="196" spans="15:15">
       <c r="O196" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="197" spans="15:15">
       <c r="O197" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="198" spans="15:15">
       <c r="O198" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="199" spans="15:15">
       <c r="O199" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="200" spans="15:15">
       <c r="O200" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="201" spans="15:15">
       <c r="O201" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="202" spans="15:15">
       <c r="O202" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="203" spans="15:15">
       <c r="O203" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="204" spans="15:15">
       <c r="O204" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="205" spans="15:15">
       <c r="O205" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="206" spans="15:15">
       <c r="O206" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="207" spans="15:15">
       <c r="O207" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="208" spans="15:15">
       <c r="O208" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="209" spans="15:15">
       <c r="O209" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="210" spans="15:15">
       <c r="O210" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="211" spans="15:15">
       <c r="O211" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="212" spans="15:15">
       <c r="O212" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="213" spans="15:15">
       <c r="O213" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="214" spans="15:15">
       <c r="O214" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="215" spans="15:15">
       <c r="O215" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="216" spans="15:15">
       <c r="O216" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="217" spans="15:15">
       <c r="O217" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="218" spans="15:15">
       <c r="O218" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="219" spans="15:15">
       <c r="O219" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="220" spans="15:15">
       <c r="O220" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="221" spans="15:15">
       <c r="O221" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="222" spans="15:15">
       <c r="O222" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="223" spans="15:15">
       <c r="O223" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="224" spans="15:15">
       <c r="O224" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="225" spans="15:15">
       <c r="O225" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="226" spans="15:15">
       <c r="O226" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="227" spans="15:15">
       <c r="O227" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="228" spans="15:15">
       <c r="O228" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="229" spans="15:15">
       <c r="O229" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="230" spans="15:15">
       <c r="O230" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="231" spans="15:15">
       <c r="O231" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="232" spans="15:15">
       <c r="O232" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="233" spans="15:15">
       <c r="O233" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="234" spans="15:15">
       <c r="O234" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="235" spans="15:15">
       <c r="O235" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="236" spans="15:15">
       <c r="O236" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="237" spans="15:15">
       <c r="O237" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="238" spans="15:15">
       <c r="O238" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="239" spans="15:15">
       <c r="O239" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="240" spans="15:15">
       <c r="O240" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="241" spans="15:15">
       <c r="O241" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="242" spans="15:15">
       <c r="O242" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="243" spans="15:15">
       <c r="O243" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="244" spans="15:15">
       <c r="O244" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="245" spans="15:15">
       <c r="O245" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="246" spans="15:15">
       <c r="O246" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="247" spans="15:15">
       <c r="O247" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="248" spans="15:15">
       <c r="O248" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="249" spans="15:15">
       <c r="O249" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="250" spans="15:15">
       <c r="O250" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="251" spans="15:15">
       <c r="O251" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="252" spans="15:15">
       <c r="O252" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="253" spans="15:15">
       <c r="O253" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="254" spans="15:15">
       <c r="O254" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="255" spans="15:15">
       <c r="O255" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="256" spans="15:15">
       <c r="O256" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="257" spans="15:15">
       <c r="O257" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="258" spans="15:15">
       <c r="O258" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="259" spans="15:15">
       <c r="O259" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="260" spans="15:15">
       <c r="O260" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="261" spans="15:15">
       <c r="O261" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="262" spans="15:15">
       <c r="O262" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="263" spans="15:15">
       <c r="O263" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="264" spans="15:15">
       <c r="O264" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="265" spans="15:15">
       <c r="O265" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="266" spans="15:15">
       <c r="O266" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="267" spans="15:15">
       <c r="O267" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="268" spans="15:15">
       <c r="O268" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="269" spans="15:15">
       <c r="O269" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="270" spans="15:15">
       <c r="O270" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="271" spans="15:15">
       <c r="O271" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="272" spans="15:15">
       <c r="O272" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="273" spans="15:15">
       <c r="O273" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="274" spans="15:15">
       <c r="O274" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="275" spans="15:15">
       <c r="O275" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="276" spans="15:15">
       <c r="O276" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="277" spans="15:15">
       <c r="O277" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="278" spans="15:15">
       <c r="O278" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="279" spans="15:15">
       <c r="O279" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="280" spans="15:15">
       <c r="O280" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="281" spans="15:15">
       <c r="O281" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="282" spans="15:15">
       <c r="O282" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="283" spans="15:15">
       <c r="O283" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="284" spans="15:15">
       <c r="O284" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="285" spans="15:15">
       <c r="O285" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="286" spans="15:15">
       <c r="O286" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="287" spans="15:15">
       <c r="O287" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="288" spans="15:15">
       <c r="O288" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="289" spans="15:15">
       <c r="O289" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000035/metadata_template_ERC000035.xlsx
+++ b/templates/ERC000035/metadata_template_ERC000035.xlsx
@@ -23,8 +23,8 @@
     <definedName name="experimentalfactor4">'cv_sample'!$AF$1:$AF$35</definedName>
     <definedName name="experimentalfactor5">'cv_sample'!$AG$1:$AG$35</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$O$1:$O$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$86</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$O$1:$O$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="813" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="650">
   <si>
     <t>alias</t>
   </si>
@@ -560,6 +560,9 @@
     <t>DNBSEQ-G50</t>
   </si>
   <si>
+    <t>DNBSEQ-G800</t>
+  </si>
+  <si>
     <t>DNBSEQ-T10x4RS</t>
   </si>
   <si>
@@ -857,1069 +860,1099 @@
     <t>(Optional) If the sample was obtained from an organism in a specific developmental stage, it is specified with this qualifier</t>
   </si>
   <si>
+    <t>organism_part</t>
+  </si>
+  <si>
+    <t>(Optional) The part of organism's anatomy or substance arising from an organism from which the biomaterial was derived, excludes cells.</t>
+  </si>
+  <si>
+    <t>ploidy</t>
+  </si>
+  <si>
+    <t>(Optional) The ploidy level of the genome (e.g. allopolyploid, haploid, diploid, triploid, tetraploid). it has implications for the downstream study of duplicated gene and regions of the genomes (and perhaps for difficulties in assembly). for terms, please select terms listed under class ploidy (pato:001374) of phenotypic quality ontology (pato), and for a browser of pato (v 2018-03-27) please refer to http://purl.bioontology.org/ontology/pato</t>
+  </si>
+  <si>
+    <t>infect</t>
+  </si>
+  <si>
+    <t>(Optional) The name of the disease causing/contaminating organism; the value can also be ‘control’.</t>
+  </si>
+  <si>
+    <t>collection_date</t>
+  </si>
+  <si>
+    <t>(Mandatory) The date the sample was collected with the intention of sequencing, either as an instance (single point in time) or interval. in case no exact time is available, the date/time can be right truncated i.e. all of these are valid iso8601 compliant times: 2008-01-23t19:23:10+00:00; 2008-01-23t19:23:10; 2008-01-23; 2008-01; 2008.</t>
+  </si>
+  <si>
+    <t>sampling_time_point</t>
+  </si>
+  <si>
+    <t>(Optional) Time point at which a sample or observation is made or taken from a biomaterial as measured from some reference point. indicate the timepoint written in iso 8601 format.</t>
+  </si>
+  <si>
+    <t>initial_time_point</t>
+  </si>
+  <si>
+    <t>(Optional) The first time point measured at the start of some process.</t>
+  </si>
+  <si>
+    <t>sex</t>
+  </si>
+  <si>
+    <t>(Optional) Sex of the organism from which the sample was obtained</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>(Recommended) Age of the organism the sample was derived from.</t>
+  </si>
+  <si>
+    <t>Afghanistan</t>
+  </si>
+  <si>
+    <t>Albania</t>
+  </si>
+  <si>
+    <t>Algeria</t>
+  </si>
+  <si>
+    <t>American Samoa</t>
+  </si>
+  <si>
+    <t>Andorra</t>
+  </si>
+  <si>
+    <t>Angola</t>
+  </si>
+  <si>
+    <t>Anguilla</t>
+  </si>
+  <si>
+    <t>Antarctica</t>
+  </si>
+  <si>
+    <t>Antigua and Barbuda</t>
+  </si>
+  <si>
+    <t>Arctic Ocean</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Armenia</t>
+  </si>
+  <si>
+    <t>Aruba</t>
+  </si>
+  <si>
+    <t>Ashmore and Cartier Islands</t>
+  </si>
+  <si>
+    <t>Atlantic Ocean</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>Austria</t>
+  </si>
+  <si>
+    <t>Azerbaijan</t>
+  </si>
+  <si>
+    <t>Bahamas</t>
+  </si>
+  <si>
+    <t>Bahrain</t>
+  </si>
+  <si>
+    <t>Baker Island</t>
+  </si>
+  <si>
+    <t>Baltic Sea</t>
+  </si>
+  <si>
+    <t>Bangladesh</t>
+  </si>
+  <si>
+    <t>Barbados</t>
+  </si>
+  <si>
+    <t>Bassas da India</t>
+  </si>
+  <si>
+    <t>Belarus</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>Belize</t>
+  </si>
+  <si>
+    <t>Benin</t>
+  </si>
+  <si>
+    <t>Bermuda</t>
+  </si>
+  <si>
+    <t>Bhutan</t>
+  </si>
+  <si>
+    <t>Bolivia</t>
+  </si>
+  <si>
+    <t>Borneo</t>
+  </si>
+  <si>
+    <t>Bosnia and Herzegovina</t>
+  </si>
+  <si>
+    <t>Botswana</t>
+  </si>
+  <si>
+    <t>Bouvet Island</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>British Virgin Islands</t>
+  </si>
+  <si>
+    <t>Brunei</t>
+  </si>
+  <si>
+    <t>Bulgaria</t>
+  </si>
+  <si>
+    <t>Burkina Faso</t>
+  </si>
+  <si>
+    <t>Burundi</t>
+  </si>
+  <si>
+    <t>Cambodia</t>
+  </si>
+  <si>
+    <t>Cameroon</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>Cape Verde</t>
+  </si>
+  <si>
+    <t>Cayman Islands</t>
+  </si>
+  <si>
+    <t>Central African Republic</t>
+  </si>
+  <si>
+    <t>Chad</t>
+  </si>
+  <si>
+    <t>Chile</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>Christmas Island</t>
+  </si>
+  <si>
+    <t>Clipperton Island</t>
+  </si>
+  <si>
+    <t>Cocos Islands</t>
+  </si>
+  <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>Comoros</t>
+  </si>
+  <si>
+    <t>Cook Islands</t>
+  </si>
+  <si>
+    <t>Coral Sea Islands</t>
+  </si>
+  <si>
+    <t>Costa Rica</t>
+  </si>
+  <si>
+    <t>Cote d'Ivoire</t>
+  </si>
+  <si>
+    <t>Croatia</t>
+  </si>
+  <si>
+    <t>Cuba</t>
+  </si>
+  <si>
+    <t>Curacao</t>
+  </si>
+  <si>
+    <t>Cyprus</t>
+  </si>
+  <si>
+    <t>Czechia</t>
+  </si>
+  <si>
+    <t>Czech Republic</t>
+  </si>
+  <si>
+    <t>Democratic Republic of the Congo</t>
+  </si>
+  <si>
+    <t>Denmark</t>
+  </si>
+  <si>
+    <t>Djibouti</t>
+  </si>
+  <si>
+    <t>Dominica</t>
+  </si>
+  <si>
+    <t>Dominican Republic</t>
+  </si>
+  <si>
+    <t>Ecuador</t>
+  </si>
+  <si>
+    <t>Egypt</t>
+  </si>
+  <si>
+    <t>El Salvador</t>
+  </si>
+  <si>
+    <t>Equatorial Guinea</t>
+  </si>
+  <si>
+    <t>Eritrea</t>
+  </si>
+  <si>
+    <t>Estonia</t>
+  </si>
+  <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
+    <t>Ethiopia</t>
+  </si>
+  <si>
+    <t>Europa Island</t>
+  </si>
+  <si>
+    <t>Falkland Islands (Islas Malvinas)</t>
+  </si>
+  <si>
+    <t>Faroe Islands</t>
+  </si>
+  <si>
+    <t>Fiji</t>
+  </si>
+  <si>
+    <t>Finland</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>French Guiana</t>
+  </si>
+  <si>
+    <t>French Polynesia</t>
+  </si>
+  <si>
+    <t>French Southern and Antarctic Lands</t>
+  </si>
+  <si>
+    <t>Gabon</t>
+  </si>
+  <si>
+    <t>Gambia</t>
+  </si>
+  <si>
+    <t>Gaza Strip</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Ghana</t>
+  </si>
+  <si>
+    <t>Gibraltar</t>
+  </si>
+  <si>
+    <t>Glorioso Islands</t>
+  </si>
+  <si>
+    <t>Greece</t>
+  </si>
+  <si>
+    <t>Greenland</t>
+  </si>
+  <si>
+    <t>Grenada</t>
+  </si>
+  <si>
+    <t>Guadeloupe</t>
+  </si>
+  <si>
+    <t>Guam</t>
+  </si>
+  <si>
+    <t>Guatemala</t>
+  </si>
+  <si>
+    <t>Guernsey</t>
+  </si>
+  <si>
+    <t>Guinea</t>
+  </si>
+  <si>
+    <t>Guinea-Bissau</t>
+  </si>
+  <si>
+    <t>Guyana</t>
+  </si>
+  <si>
+    <t>Haiti</t>
+  </si>
+  <si>
+    <t>Heard Island and McDonald Islands</t>
+  </si>
+  <si>
+    <t>Honduras</t>
+  </si>
+  <si>
+    <t>Hong Kong</t>
+  </si>
+  <si>
+    <t>Howland Island</t>
+  </si>
+  <si>
+    <t>Hungary</t>
+  </si>
+  <si>
+    <t>Iceland</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Indian Ocean</t>
+  </si>
+  <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t>Iran</t>
+  </si>
+  <si>
+    <t>Iraq</t>
+  </si>
+  <si>
+    <t>Ireland</t>
+  </si>
+  <si>
+    <t>Isle of Man</t>
+  </si>
+  <si>
+    <t>Israel</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>Jamaica</t>
+  </si>
+  <si>
+    <t>Jan Mayen</t>
+  </si>
+  <si>
+    <t>Japan</t>
+  </si>
+  <si>
+    <t>Jarvis Island</t>
+  </si>
+  <si>
+    <t>Jersey</t>
+  </si>
+  <si>
+    <t>Johnston Atoll</t>
+  </si>
+  <si>
+    <t>Jordan</t>
+  </si>
+  <si>
+    <t>Juan de Nova Island</t>
+  </si>
+  <si>
+    <t>Kazakhstan</t>
+  </si>
+  <si>
+    <t>Kenya</t>
+  </si>
+  <si>
+    <t>Kerguelen Archipelago</t>
+  </si>
+  <si>
+    <t>Kingman Reef</t>
+  </si>
+  <si>
+    <t>Kiribati</t>
+  </si>
+  <si>
+    <t>Kosovo</t>
+  </si>
+  <si>
+    <t>Kuwait</t>
+  </si>
+  <si>
+    <t>Kyrgyzstan</t>
+  </si>
+  <si>
+    <t>Laos</t>
+  </si>
+  <si>
+    <t>Latvia</t>
+  </si>
+  <si>
+    <t>Lebanon</t>
+  </si>
+  <si>
+    <t>Lesotho</t>
+  </si>
+  <si>
+    <t>Liberia</t>
+  </si>
+  <si>
+    <t>Libya</t>
+  </si>
+  <si>
+    <t>Liechtenstein</t>
+  </si>
+  <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
+    <t>Lithuania</t>
+  </si>
+  <si>
+    <t>Luxembourg</t>
+  </si>
+  <si>
+    <t>Macau</t>
+  </si>
+  <si>
+    <t>Madagascar</t>
+  </si>
+  <si>
+    <t>Malawi</t>
+  </si>
+  <si>
+    <t>Malaysia</t>
+  </si>
+  <si>
+    <t>Maldives</t>
+  </si>
+  <si>
+    <t>Mali</t>
+  </si>
+  <si>
+    <t>Malta</t>
+  </si>
+  <si>
+    <t>Marshall Islands</t>
+  </si>
+  <si>
+    <t>Martinique</t>
+  </si>
+  <si>
+    <t>Mauritania</t>
+  </si>
+  <si>
+    <t>Mauritius</t>
+  </si>
+  <si>
+    <t>Mayotte</t>
+  </si>
+  <si>
+    <t>Mediterranean Sea</t>
+  </si>
+  <si>
+    <t>Mexico</t>
+  </si>
+  <si>
+    <t>Micronesia, Federated States of</t>
+  </si>
+  <si>
+    <t>Midway Islands</t>
+  </si>
+  <si>
+    <t>Moldova</t>
+  </si>
+  <si>
+    <t>Monaco</t>
+  </si>
+  <si>
+    <t>Mongolia</t>
+  </si>
+  <si>
+    <t>Montenegro</t>
+  </si>
+  <si>
+    <t>Montserrat</t>
+  </si>
+  <si>
+    <t>Morocco</t>
+  </si>
+  <si>
+    <t>Mozambique</t>
+  </si>
+  <si>
+    <t>Myanmar</t>
+  </si>
+  <si>
+    <t>Namibia</t>
+  </si>
+  <si>
+    <t>Nauru</t>
+  </si>
+  <si>
+    <t>Navassa Island</t>
+  </si>
+  <si>
+    <t>Nepal</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>New Caledonia</t>
+  </si>
+  <si>
+    <t>New Zealand</t>
+  </si>
+  <si>
+    <t>Nicaragua</t>
+  </si>
+  <si>
+    <t>Niger</t>
+  </si>
+  <si>
+    <t>Nigeria</t>
+  </si>
+  <si>
+    <t>Niue</t>
+  </si>
+  <si>
+    <t>Norfolk Island</t>
+  </si>
+  <si>
+    <t>North Korea</t>
+  </si>
+  <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
+    <t>North Sea</t>
+  </si>
+  <si>
+    <t>Northern Mariana Islands</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t>Oman</t>
+  </si>
+  <si>
+    <t>Pacific Ocean</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>Palau</t>
+  </si>
+  <si>
+    <t>Palmyra Atoll</t>
+  </si>
+  <si>
+    <t>Panama</t>
+  </si>
+  <si>
+    <t>Papua New Guinea</t>
+  </si>
+  <si>
+    <t>Paracel Islands</t>
+  </si>
+  <si>
+    <t>Paraguay</t>
+  </si>
+  <si>
+    <t>Peru</t>
+  </si>
+  <si>
+    <t>Philippines</t>
+  </si>
+  <si>
+    <t>Pitcairn Islands</t>
+  </si>
+  <si>
+    <t>Poland</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>Puerto Rico</t>
+  </si>
+  <si>
+    <t>Qatar</t>
+  </si>
+  <si>
+    <t>Republic of the Congo</t>
+  </si>
+  <si>
+    <t>Reunion</t>
+  </si>
+  <si>
+    <t>Romania</t>
+  </si>
+  <si>
+    <t>Ross Sea</t>
+  </si>
+  <si>
+    <t>Russia</t>
+  </si>
+  <si>
+    <t>Rwanda</t>
+  </si>
+  <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
+    <t>Saint Helena</t>
+  </si>
+  <si>
+    <t>Saint Kitts and Nevis</t>
+  </si>
+  <si>
+    <t>Saint Lucia</t>
+  </si>
+  <si>
+    <t>Saint Pierre and Miquelon</t>
+  </si>
+  <si>
+    <t>Saint Vincent and the Grenadines</t>
+  </si>
+  <si>
+    <t>Samoa</t>
+  </si>
+  <si>
+    <t>San Marino</t>
+  </si>
+  <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
+    <t>Sao Tome and Principe</t>
+  </si>
+  <si>
+    <t>Saudi Arabia</t>
+  </si>
+  <si>
+    <t>Senegal</t>
+  </si>
+  <si>
+    <t>Serbia</t>
+  </si>
+  <si>
+    <t>Seychelles</t>
+  </si>
+  <si>
+    <t>Sierra Leone</t>
+  </si>
+  <si>
+    <t>Singapore</t>
+  </si>
+  <si>
+    <t>Sint Maarten</t>
+  </si>
+  <si>
+    <t>Slovakia</t>
+  </si>
+  <si>
+    <t>Slovenia</t>
+  </si>
+  <si>
+    <t>Solomon Islands</t>
+  </si>
+  <si>
+    <t>Somalia</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
+    <t>South Georgia and the South Sandwich Islands</t>
+  </si>
+  <si>
+    <t>South Korea</t>
+  </si>
+  <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
+    <t>Southern Ocean</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Spratly Islands</t>
+  </si>
+  <si>
+    <t>Sri Lanka</t>
+  </si>
+  <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
+    <t>Sudan</t>
+  </si>
+  <si>
+    <t>Suriname</t>
+  </si>
+  <si>
+    <t>Svalbard</t>
+  </si>
+  <si>
+    <t>Sweden</t>
+  </si>
+  <si>
+    <t>Switzerland</t>
+  </si>
+  <si>
+    <t>Syria</t>
+  </si>
+  <si>
+    <t>Taiwan</t>
+  </si>
+  <si>
+    <t>Tajikistan</t>
+  </si>
+  <si>
+    <t>Tanzania</t>
+  </si>
+  <si>
+    <t>Tasman Sea</t>
+  </si>
+  <si>
+    <t>Thailand</t>
+  </si>
+  <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
+    <t>Togo</t>
+  </si>
+  <si>
+    <t>Tokelau</t>
+  </si>
+  <si>
+    <t>Tonga</t>
+  </si>
+  <si>
+    <t>Trinidad and Tobago</t>
+  </si>
+  <si>
+    <t>Tromelin Island</t>
+  </si>
+  <si>
+    <t>Tunisia</t>
+  </si>
+  <si>
+    <t>Turkey</t>
+  </si>
+  <si>
+    <t>Turkmenistan</t>
+  </si>
+  <si>
+    <t>Turks and Caicos Islands</t>
+  </si>
+  <si>
+    <t>Tuvalu</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
+    <t>Uganda</t>
+  </si>
+  <si>
+    <t>Ukraine</t>
+  </si>
+  <si>
+    <t>United Arab Emirates</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>Uruguay</t>
+  </si>
+  <si>
+    <t>Uzbekistan</t>
+  </si>
+  <si>
+    <t>Vanuatu</t>
+  </si>
+  <si>
+    <t>Venezuela</t>
+  </si>
+  <si>
+    <t>Viet Nam</t>
+  </si>
+  <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
+    <t>Virgin Islands</t>
+  </si>
+  <si>
+    <t>Wallis and Futuna</t>
+  </si>
+  <si>
+    <t>West Bank</t>
+  </si>
+  <si>
+    <t>Western Sahara</t>
+  </si>
+  <si>
+    <t>Yemen</t>
+  </si>
+  <si>
+    <t>Zambia</t>
+  </si>
+  <si>
+    <t>Zimbabwe</t>
+  </si>
+  <si>
+    <t>missing</t>
+  </si>
+  <si>
+    <t>missing: control sample</t>
+  </si>
+  <si>
+    <t>missing: data agreement established pre-2023</t>
+  </si>
+  <si>
+    <t>missing: endangered species</t>
+  </si>
+  <si>
+    <t>missing: human-identifiable</t>
+  </si>
+  <si>
+    <t>missing: lab stock</t>
+  </si>
+  <si>
+    <t>missing: sample group</t>
+  </si>
+  <si>
+    <t>missing: synthetic construct</t>
+  </si>
+  <si>
+    <t>missing: third party data</t>
+  </si>
+  <si>
+    <t>not applicable</t>
+  </si>
+  <si>
+    <t>not collected</t>
+  </si>
+  <si>
+    <t>not provided</t>
+  </si>
+  <si>
+    <t>restricted access</t>
+  </si>
+  <si>
+    <t>geographic_location_country_andor_sea</t>
+  </si>
+  <si>
+    <t>(Mandatory) The geographical origin of where the sample was collected from, with the intention of sequencing, as defined by the country or sea name. country or sea names should be chosen from the insdc country list (http://insdc.org/country.html).</t>
+  </si>
+  <si>
+    <t>phenotype</t>
+  </si>
+  <si>
+    <t>(Optional) Where possible, please use the experimental factor ontology (efo) to describe your phenotypes.</t>
+  </si>
+  <si>
+    <t>cellular_component</t>
+  </si>
+  <si>
+    <t>(Optional) The part of a cell or its extracellular environment in which a gene product is located.</t>
+  </si>
+  <si>
+    <t>individual</t>
+  </si>
+  <si>
+    <t>(Optional) An individual used a specimen in an experiment, from which a material sample was derived.</t>
+  </si>
+  <si>
+    <t>disease_staging</t>
+  </si>
+  <si>
+    <t>(Optional) The stage or progression of a disease in an organism. includes pathological staging of cancers and other disease progression. e.g. dukes c stage describing colon cancer (efo_0000410).</t>
+  </si>
+  <si>
+    <t>immunoprecipitate</t>
+  </si>
+  <si>
+    <t>(Optional) The precipitate antibody bound target molecules generated when precipitating an antigen out of a solution during the process of immunoprecipitation.</t>
+  </si>
+  <si>
+    <t>replicate</t>
+  </si>
+  <si>
+    <t>(Optional) A role played by a biological sample in the context of an experiment where the intent is that biological or technical variation is measured.</t>
+  </si>
+  <si>
+    <t>cultivar</t>
+  </si>
+  <si>
+    <t>(Optional) Cultivar (cultivated variety) of plant from which sample was obtained</t>
+  </si>
+  <si>
+    <t>ecotype</t>
+  </si>
+  <si>
+    <t>(Optional) A population within a given species displaying genetically based, phenotypic traits that reflect adaptation to a local habitat.</t>
+  </si>
+  <si>
+    <t>cell_line</t>
+  </si>
+  <si>
+    <t>(Optional) Cell line from which the sample was obtained</t>
+  </si>
+  <si>
+    <t>strain</t>
+  </si>
+  <si>
+    <t>(Optional) Name of the strain from which the sample was obtained.</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>(Optional) The duration in which the treatment has occurred.</t>
+  </si>
+  <si>
+    <t>dose</t>
+  </si>
+  <si>
+    <t>(Optional) The total quantity or strength of a substance administered at one time.</t>
+  </si>
+  <si>
+    <t>chemical_compound</t>
+  </si>
+  <si>
+    <t>(Optional) A drug, solvent, chemical, etc., with a property that can be measured such as concentration (http://purl.obolibrary.org/obo/chebi_37577).</t>
+  </si>
+  <si>
+    <t>RNA</t>
+  </si>
+  <si>
+    <t>block</t>
+  </si>
+  <si>
+    <t>cell line</t>
+  </si>
+  <si>
+    <t>cell type</t>
+  </si>
+  <si>
+    <t>chemical compound</t>
+  </si>
+  <si>
+    <t>disease staging</t>
+  </si>
+  <si>
+    <t>environmental history</t>
+  </si>
+  <si>
+    <t>environmental stress</t>
+  </si>
+  <si>
+    <t>genotype</t>
+  </si>
+  <si>
+    <t>growth condition</t>
+  </si>
+  <si>
+    <t>initial time point</t>
+  </si>
+  <si>
+    <t>organism</t>
+  </si>
+  <si>
     <t>organism part</t>
   </si>
   <si>
-    <t>(Optional) The part of organism's anatomy or substance arising from an organism from which the biomaterial was derived, excludes cells.</t>
-  </si>
-  <si>
-    <t>ploidy</t>
-  </si>
-  <si>
-    <t>(Optional) The ploidy level of the genome (e.g. allopolyploid, haploid, diploid, triploid, tetraploid). it has implications for the downstream study of duplicated gene and regions of the genomes (and perhaps for difficulties in assembly). for terms, please select terms listed under class ploidy (pato:001374) of phenotypic quality ontology (pato), and for a browser of pato (v 2018-03-27) please refer to http://purl.bioontology.org/ontology/pato</t>
-  </si>
-  <si>
-    <t>infect</t>
-  </si>
-  <si>
-    <t>(Optional) The name of the disease causing/contaminating organism; the value can also be ‘control’.</t>
-  </si>
-  <si>
-    <t>collection date</t>
-  </si>
-  <si>
-    <t>(Mandatory) The date the sample was collected with the intention of sequencing, either as an instance (single point in time) or interval. in case no exact time is available, the date/time can be right truncated i.e. all of these are valid iso8601 compliant times: 2008-01-23t19:23:10+00:00; 2008-01-23t19:23:10; 2008-01-23; 2008-01; 2008.</t>
+    <t>protein-bound</t>
+  </si>
+  <si>
+    <t>protocol</t>
+  </si>
+  <si>
+    <t>rnase</t>
+  </si>
+  <si>
+    <t>sample type</t>
+  </si>
+  <si>
+    <t>sampling site</t>
   </si>
   <si>
     <t>sampling time point</t>
   </si>
   <si>
-    <t>(Optional) Time point at which a sample or observation is made or taken from a biomaterial as measured from some reference point. indicate the timepoint written in iso 8601 format.</t>
-  </si>
-  <si>
-    <t>initial time point</t>
-  </si>
-  <si>
-    <t>(Optional) The first time point measured at the start of some process.</t>
-  </si>
-  <si>
-    <t>sex</t>
-  </si>
-  <si>
-    <t>(Optional) Sex of the organism from which the sample was obtained</t>
-  </si>
-  <si>
-    <t>age</t>
-  </si>
-  <si>
-    <t>(Recommended) Age of the organism the sample was derived from.</t>
-  </si>
-  <si>
-    <t>Afghanistan</t>
-  </si>
-  <si>
-    <t>Albania</t>
-  </si>
-  <si>
-    <t>Algeria</t>
-  </si>
-  <si>
-    <t>American Samoa</t>
-  </si>
-  <si>
-    <t>Andorra</t>
-  </si>
-  <si>
-    <t>Angola</t>
-  </si>
-  <si>
-    <t>Anguilla</t>
-  </si>
-  <si>
-    <t>Antarctica</t>
-  </si>
-  <si>
-    <t>Antigua and Barbuda</t>
-  </si>
-  <si>
-    <t>Arctic Ocean</t>
-  </si>
-  <si>
-    <t>Argentina</t>
-  </si>
-  <si>
-    <t>Armenia</t>
-  </si>
-  <si>
-    <t>Aruba</t>
-  </si>
-  <si>
-    <t>Ashmore and Cartier Islands</t>
-  </si>
-  <si>
-    <t>Atlantic Ocean</t>
-  </si>
-  <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>Austria</t>
-  </si>
-  <si>
-    <t>Azerbaijan</t>
-  </si>
-  <si>
-    <t>Bahamas</t>
-  </si>
-  <si>
-    <t>Bahrain</t>
-  </si>
-  <si>
-    <t>Baker Island</t>
-  </si>
-  <si>
-    <t>Baltic Sea</t>
-  </si>
-  <si>
-    <t>Bangladesh</t>
-  </si>
-  <si>
-    <t>Barbados</t>
-  </si>
-  <si>
-    <t>Bassas da India</t>
-  </si>
-  <si>
-    <t>Belarus</t>
-  </si>
-  <si>
-    <t>Belgium</t>
-  </si>
-  <si>
-    <t>Belize</t>
-  </si>
-  <si>
-    <t>Benin</t>
-  </si>
-  <si>
-    <t>Bermuda</t>
-  </si>
-  <si>
-    <t>Bhutan</t>
-  </si>
-  <si>
-    <t>Bolivia</t>
-  </si>
-  <si>
-    <t>Borneo</t>
-  </si>
-  <si>
-    <t>Bosnia and Herzegovina</t>
-  </si>
-  <si>
-    <t>Botswana</t>
-  </si>
-  <si>
-    <t>Bouvet Island</t>
-  </si>
-  <si>
-    <t>Brazil</t>
-  </si>
-  <si>
-    <t>British Virgin Islands</t>
-  </si>
-  <si>
-    <t>Brunei</t>
-  </si>
-  <si>
-    <t>Bulgaria</t>
-  </si>
-  <si>
-    <t>Burkina Faso</t>
-  </si>
-  <si>
-    <t>Burundi</t>
-  </si>
-  <si>
-    <t>Cambodia</t>
-  </si>
-  <si>
-    <t>Cameroon</t>
-  </si>
-  <si>
-    <t>Canada</t>
-  </si>
-  <si>
-    <t>Cape Verde</t>
-  </si>
-  <si>
-    <t>Cayman Islands</t>
-  </si>
-  <si>
-    <t>Central African Republic</t>
-  </si>
-  <si>
-    <t>Chad</t>
-  </si>
-  <si>
-    <t>Chile</t>
-  </si>
-  <si>
-    <t>China</t>
-  </si>
-  <si>
-    <t>Christmas Island</t>
-  </si>
-  <si>
-    <t>Clipperton Island</t>
-  </si>
-  <si>
-    <t>Cocos Islands</t>
-  </si>
-  <si>
-    <t>Colombia</t>
-  </si>
-  <si>
-    <t>Comoros</t>
-  </si>
-  <si>
-    <t>Cook Islands</t>
-  </si>
-  <si>
-    <t>Coral Sea Islands</t>
-  </si>
-  <si>
-    <t>Costa Rica</t>
-  </si>
-  <si>
-    <t>Cote d'Ivoire</t>
-  </si>
-  <si>
-    <t>Croatia</t>
-  </si>
-  <si>
-    <t>Cuba</t>
-  </si>
-  <si>
-    <t>Curacao</t>
-  </si>
-  <si>
-    <t>Cyprus</t>
-  </si>
-  <si>
-    <t>Czechia</t>
-  </si>
-  <si>
-    <t>Czech Republic</t>
-  </si>
-  <si>
-    <t>Democratic Republic of the Congo</t>
-  </si>
-  <si>
-    <t>Denmark</t>
-  </si>
-  <si>
-    <t>Djibouti</t>
-  </si>
-  <si>
-    <t>Dominica</t>
-  </si>
-  <si>
-    <t>Dominican Republic</t>
-  </si>
-  <si>
-    <t>East Timor</t>
-  </si>
-  <si>
-    <t>Ecuador</t>
-  </si>
-  <si>
-    <t>Egypt</t>
-  </si>
-  <si>
-    <t>El Salvador</t>
-  </si>
-  <si>
-    <t>Equatorial Guinea</t>
-  </si>
-  <si>
-    <t>Eritrea</t>
-  </si>
-  <si>
-    <t>Estonia</t>
-  </si>
-  <si>
-    <t>Ethiopia</t>
-  </si>
-  <si>
-    <t>Europa Island</t>
-  </si>
-  <si>
-    <t>Falkland Islands (Islas Malvinas)</t>
-  </si>
-  <si>
-    <t>Faroe Islands</t>
-  </si>
-  <si>
-    <t>Fiji</t>
-  </si>
-  <si>
-    <t>Finland</t>
-  </si>
-  <si>
-    <t>France</t>
-  </si>
-  <si>
-    <t>French Guiana</t>
-  </si>
-  <si>
-    <t>French Polynesia</t>
-  </si>
-  <si>
-    <t>French Southern and Antarctic Lands</t>
-  </si>
-  <si>
-    <t>Gabon</t>
-  </si>
-  <si>
-    <t>Gambia</t>
-  </si>
-  <si>
-    <t>Gaza Strip</t>
-  </si>
-  <si>
-    <t>Georgia</t>
-  </si>
-  <si>
-    <t>Germany</t>
-  </si>
-  <si>
-    <t>Ghana</t>
-  </si>
-  <si>
-    <t>Gibraltar</t>
-  </si>
-  <si>
-    <t>Glorioso Islands</t>
-  </si>
-  <si>
-    <t>Greece</t>
-  </si>
-  <si>
-    <t>Greenland</t>
-  </si>
-  <si>
-    <t>Grenada</t>
-  </si>
-  <si>
-    <t>Guadeloupe</t>
-  </si>
-  <si>
-    <t>Guam</t>
-  </si>
-  <si>
-    <t>Guatemala</t>
-  </si>
-  <si>
-    <t>Guernsey</t>
-  </si>
-  <si>
-    <t>Guinea</t>
-  </si>
-  <si>
-    <t>Guinea-Bissau</t>
-  </si>
-  <si>
-    <t>Guyana</t>
-  </si>
-  <si>
-    <t>Haiti</t>
-  </si>
-  <si>
-    <t>Heard Island and McDonald Islands</t>
-  </si>
-  <si>
-    <t>Honduras</t>
-  </si>
-  <si>
-    <t>Hong Kong</t>
-  </si>
-  <si>
-    <t>Howland Island</t>
-  </si>
-  <si>
-    <t>Hungary</t>
-  </si>
-  <si>
-    <t>Iceland</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Indian Ocean</t>
-  </si>
-  <si>
-    <t>Indonesia</t>
-  </si>
-  <si>
-    <t>Iran</t>
-  </si>
-  <si>
-    <t>Iraq</t>
-  </si>
-  <si>
-    <t>Ireland</t>
-  </si>
-  <si>
-    <t>Isle of Man</t>
-  </si>
-  <si>
-    <t>Israel</t>
-  </si>
-  <si>
-    <t>Italy</t>
-  </si>
-  <si>
-    <t>Jamaica</t>
-  </si>
-  <si>
-    <t>Jan Mayen</t>
-  </si>
-  <si>
-    <t>Japan</t>
-  </si>
-  <si>
-    <t>Jarvis Island</t>
-  </si>
-  <si>
-    <t>Jersey</t>
-  </si>
-  <si>
-    <t>Johnston Atoll</t>
-  </si>
-  <si>
-    <t>Jordan</t>
-  </si>
-  <si>
-    <t>Juan de Nova Island</t>
-  </si>
-  <si>
-    <t>Kazakhstan</t>
-  </si>
-  <si>
-    <t>Kenya</t>
-  </si>
-  <si>
-    <t>Kerguelen Archipelago</t>
-  </si>
-  <si>
-    <t>Kingman Reef</t>
-  </si>
-  <si>
-    <t>Kiribati</t>
-  </si>
-  <si>
-    <t>Kosovo</t>
-  </si>
-  <si>
-    <t>Kuwait</t>
-  </si>
-  <si>
-    <t>Kyrgyzstan</t>
-  </si>
-  <si>
-    <t>Laos</t>
-  </si>
-  <si>
-    <t>Latvia</t>
-  </si>
-  <si>
-    <t>Lebanon</t>
-  </si>
-  <si>
-    <t>Lesotho</t>
-  </si>
-  <si>
-    <t>Liberia</t>
-  </si>
-  <si>
-    <t>Libya</t>
-  </si>
-  <si>
-    <t>Liechtenstein</t>
-  </si>
-  <si>
-    <t>Lithuania</t>
-  </si>
-  <si>
-    <t>Luxembourg</t>
-  </si>
-  <si>
-    <t>Macau</t>
-  </si>
-  <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
-    <t>Madagascar</t>
-  </si>
-  <si>
-    <t>Malawi</t>
-  </si>
-  <si>
-    <t>Malaysia</t>
-  </si>
-  <si>
-    <t>Maldives</t>
-  </si>
-  <si>
-    <t>Mali</t>
-  </si>
-  <si>
-    <t>Malta</t>
-  </si>
-  <si>
-    <t>Marshall Islands</t>
-  </si>
-  <si>
-    <t>Martinique</t>
-  </si>
-  <si>
-    <t>Mauritania</t>
-  </si>
-  <si>
-    <t>Mauritius</t>
-  </si>
-  <si>
-    <t>Mayotte</t>
-  </si>
-  <si>
-    <t>Mediterranean Sea</t>
-  </si>
-  <si>
-    <t>Mexico</t>
-  </si>
-  <si>
-    <t>Micronesia</t>
-  </si>
-  <si>
-    <t>Midway Islands</t>
-  </si>
-  <si>
-    <t>Moldova</t>
-  </si>
-  <si>
-    <t>Monaco</t>
-  </si>
-  <si>
-    <t>Mongolia</t>
-  </si>
-  <si>
-    <t>Montenegro</t>
-  </si>
-  <si>
-    <t>Montserrat</t>
-  </si>
-  <si>
-    <t>Morocco</t>
-  </si>
-  <si>
-    <t>Mozambique</t>
-  </si>
-  <si>
-    <t>Myanmar</t>
-  </si>
-  <si>
-    <t>Namibia</t>
-  </si>
-  <si>
-    <t>Nauru</t>
-  </si>
-  <si>
-    <t>Navassa Island</t>
-  </si>
-  <si>
-    <t>Nepal</t>
-  </si>
-  <si>
-    <t>Netherlands</t>
-  </si>
-  <si>
-    <t>New Caledonia</t>
-  </si>
-  <si>
-    <t>New Zealand</t>
-  </si>
-  <si>
-    <t>Nicaragua</t>
-  </si>
-  <si>
-    <t>Niger</t>
-  </si>
-  <si>
-    <t>Nigeria</t>
-  </si>
-  <si>
-    <t>Niue</t>
-  </si>
-  <si>
-    <t>Norfolk Island</t>
-  </si>
-  <si>
-    <t>North Korea</t>
-  </si>
-  <si>
-    <t>North Sea</t>
-  </si>
-  <si>
-    <t>Northern Mariana Islands</t>
-  </si>
-  <si>
-    <t>Norway</t>
-  </si>
-  <si>
-    <t>Oman</t>
-  </si>
-  <si>
-    <t>Pacific Ocean</t>
-  </si>
-  <si>
-    <t>Pakistan</t>
-  </si>
-  <si>
-    <t>Palau</t>
-  </si>
-  <si>
-    <t>Palmyra Atoll</t>
-  </si>
-  <si>
-    <t>Panama</t>
-  </si>
-  <si>
-    <t>Papua New Guinea</t>
-  </si>
-  <si>
-    <t>Paracel Islands</t>
-  </si>
-  <si>
-    <t>Paraguay</t>
-  </si>
-  <si>
-    <t>Peru</t>
-  </si>
-  <si>
-    <t>Philippines</t>
-  </si>
-  <si>
-    <t>Pitcairn Islands</t>
-  </si>
-  <si>
-    <t>Poland</t>
-  </si>
-  <si>
-    <t>Portugal</t>
-  </si>
-  <si>
-    <t>Puerto Rico</t>
-  </si>
-  <si>
-    <t>Qatar</t>
-  </si>
-  <si>
-    <t>Republic of the Congo</t>
-  </si>
-  <si>
-    <t>Reunion</t>
-  </si>
-  <si>
-    <t>Romania</t>
-  </si>
-  <si>
-    <t>Ross Sea</t>
-  </si>
-  <si>
-    <t>Russia</t>
-  </si>
-  <si>
-    <t>Rwanda</t>
-  </si>
-  <si>
-    <t>Saint Helena</t>
-  </si>
-  <si>
-    <t>Saint Kitts and Nevis</t>
-  </si>
-  <si>
-    <t>Saint Lucia</t>
-  </si>
-  <si>
-    <t>Saint Pierre and Miquelon</t>
-  </si>
-  <si>
-    <t>Saint Vincent and the Grenadines</t>
-  </si>
-  <si>
-    <t>Samoa</t>
-  </si>
-  <si>
-    <t>San Marino</t>
-  </si>
-  <si>
-    <t>Sao Tome and Principe</t>
-  </si>
-  <si>
-    <t>Saudi Arabia</t>
-  </si>
-  <si>
-    <t>Senegal</t>
-  </si>
-  <si>
-    <t>Serbia</t>
-  </si>
-  <si>
-    <t>Seychelles</t>
-  </si>
-  <si>
-    <t>Sierra Leone</t>
-  </si>
-  <si>
-    <t>Singapore</t>
-  </si>
-  <si>
-    <t>Sint Maarten</t>
-  </si>
-  <si>
-    <t>Slovakia</t>
-  </si>
-  <si>
-    <t>Slovenia</t>
-  </si>
-  <si>
-    <t>Solomon Islands</t>
-  </si>
-  <si>
-    <t>Somalia</t>
-  </si>
-  <si>
-    <t>South Africa</t>
-  </si>
-  <si>
-    <t>South Georgia and the South Sandwich Islands</t>
-  </si>
-  <si>
-    <t>South Korea</t>
-  </si>
-  <si>
-    <t>Southern Ocean</t>
-  </si>
-  <si>
-    <t>Spain</t>
-  </si>
-  <si>
-    <t>Spratly Islands</t>
-  </si>
-  <si>
-    <t>Sri Lanka</t>
-  </si>
-  <si>
-    <t>Sudan</t>
-  </si>
-  <si>
-    <t>Suriname</t>
-  </si>
-  <si>
-    <t>Svalbard</t>
-  </si>
-  <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
-    <t>Sweden</t>
-  </si>
-  <si>
-    <t>Switzerland</t>
-  </si>
-  <si>
-    <t>Syria</t>
-  </si>
-  <si>
-    <t>Taiwan</t>
-  </si>
-  <si>
-    <t>Tajikistan</t>
-  </si>
-  <si>
-    <t>Tanzania</t>
-  </si>
-  <si>
-    <t>Tasman Sea</t>
-  </si>
-  <si>
-    <t>Thailand</t>
-  </si>
-  <si>
-    <t>Togo</t>
-  </si>
-  <si>
-    <t>Tokelau</t>
-  </si>
-  <si>
-    <t>Tonga</t>
-  </si>
-  <si>
-    <t>Trinidad and Tobago</t>
-  </si>
-  <si>
-    <t>Tromelin Island</t>
-  </si>
-  <si>
-    <t>Tunisia</t>
-  </si>
-  <si>
-    <t>Turkey</t>
-  </si>
-  <si>
-    <t>Turkmenistan</t>
-  </si>
-  <si>
-    <t>Turks and Caicos Islands</t>
-  </si>
-  <si>
-    <t>Tuvalu</t>
-  </si>
-  <si>
-    <t>USA</t>
-  </si>
-  <si>
-    <t>Uganda</t>
-  </si>
-  <si>
-    <t>Ukraine</t>
-  </si>
-  <si>
-    <t>United Arab Emirates</t>
-  </si>
-  <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>Uruguay</t>
-  </si>
-  <si>
-    <t>Uzbekistan</t>
-  </si>
-  <si>
-    <t>Vanuatu</t>
-  </si>
-  <si>
-    <t>Venezuela</t>
-  </si>
-  <si>
-    <t>Viet Nam</t>
-  </si>
-  <si>
-    <t>Virgin Islands</t>
-  </si>
-  <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
-    <t>Wallis and Futuna</t>
-  </si>
-  <si>
-    <t>West Bank</t>
-  </si>
-  <si>
-    <t>Western Sahara</t>
-  </si>
-  <si>
-    <t>Yemen</t>
-  </si>
-  <si>
-    <t>Zambia</t>
-  </si>
-  <si>
-    <t>Zimbabwe</t>
-  </si>
-  <si>
-    <t>missing</t>
-  </si>
-  <si>
-    <t>missing: control sample</t>
-  </si>
-  <si>
-    <t>missing: data agreement established pre-2023</t>
-  </si>
-  <si>
-    <t>missing: endangered species</t>
-  </si>
-  <si>
-    <t>missing: human-identifiable</t>
-  </si>
-  <si>
-    <t>missing: lab stock</t>
-  </si>
-  <si>
-    <t>missing: sample group</t>
-  </si>
-  <si>
-    <t>missing: synthetic construct</t>
-  </si>
-  <si>
-    <t>missing: third party data</t>
-  </si>
-  <si>
-    <t>not applicable</t>
-  </si>
-  <si>
-    <t>not collected</t>
-  </si>
-  <si>
-    <t>not provided</t>
-  </si>
-  <si>
-    <t>restricted access</t>
-  </si>
-  <si>
-    <t>geographic location (country and/or sea)</t>
-  </si>
-  <si>
-    <t>(Mandatory) The geographical origin of where the sample was collected from, with the intention of sequencing, as defined by the country or sea name. country or sea names should be chosen from the insdc country list (http://insdc.org/country.html).</t>
-  </si>
-  <si>
-    <t>phenotype</t>
-  </si>
-  <si>
-    <t>(Optional) Where possible, please use the experimental factor ontology (efo) to describe your phenotypes.</t>
-  </si>
-  <si>
-    <t>cellular component</t>
-  </si>
-  <si>
-    <t>(Optional) The part of a cell or its extracellular environment in which a gene product is located.</t>
-  </si>
-  <si>
-    <t>individual</t>
-  </si>
-  <si>
-    <t>(Optional) An individual used a specimen in an experiment, from which a material sample was derived.</t>
-  </si>
-  <si>
-    <t>disease staging</t>
-  </si>
-  <si>
-    <t>(Optional) The stage or progression of a disease in an organism. includes pathological staging of cancers and other disease progression. e.g. dukes c stage describing colon cancer (efo_0000410).</t>
-  </si>
-  <si>
-    <t>immunoprecipitate</t>
-  </si>
-  <si>
-    <t>(Optional) The precipitate antibody bound target molecules generated when precipitating an antigen out of a solution during the process of immunoprecipitation.</t>
-  </si>
-  <si>
-    <t>replicate</t>
-  </si>
-  <si>
-    <t>(Optional) A role played by a biological sample in the context of an experiment where the intent is that biological or technical variation is measured.</t>
-  </si>
-  <si>
-    <t>cultivar</t>
-  </si>
-  <si>
-    <t>(Optional) Cultivar (cultivated variety) of plant from which sample was obtained</t>
-  </si>
-  <si>
-    <t>ecotype</t>
-  </si>
-  <si>
-    <t>(Optional) A population within a given species displaying genetically based, phenotypic traits that reflect adaptation to a local habitat.</t>
-  </si>
-  <si>
-    <t>cell_line</t>
-  </si>
-  <si>
-    <t>(Optional) Cell line from which the sample was obtained</t>
-  </si>
-  <si>
-    <t>strain</t>
-  </si>
-  <si>
-    <t>(Optional) Name of the strain from which the sample was obtained.</t>
-  </si>
-  <si>
-    <t>time</t>
-  </si>
-  <si>
-    <t>(Optional) The duration in which the treatment has occurred.</t>
-  </si>
-  <si>
-    <t>dose</t>
-  </si>
-  <si>
-    <t>(Optional) The total quantity or strength of a substance administered at one time.</t>
-  </si>
-  <si>
-    <t>chemical compound</t>
-  </si>
-  <si>
-    <t>(Optional) A drug, solvent, chemical, etc., with a property that can be measured such as concentration (http://purl.obolibrary.org/obo/chebi_37577).</t>
-  </si>
-  <si>
-    <t>RNA</t>
-  </si>
-  <si>
-    <t>block</t>
-  </si>
-  <si>
-    <t>cell line</t>
-  </si>
-  <si>
-    <t>cell type</t>
-  </si>
-  <si>
-    <t>environmental history</t>
-  </si>
-  <si>
-    <t>environmental stress</t>
-  </si>
-  <si>
-    <t>genotype</t>
-  </si>
-  <si>
-    <t>growth condition</t>
-  </si>
-  <si>
-    <t>organism</t>
-  </si>
-  <si>
-    <t>protein-bound</t>
-  </si>
-  <si>
-    <t>protocol</t>
-  </si>
-  <si>
-    <t>rnase</t>
-  </si>
-  <si>
-    <t>sample type</t>
-  </si>
-  <si>
-    <t>sampling site</t>
-  </si>
-  <si>
     <t>temperature</t>
   </si>
   <si>
     <t>transgene</t>
   </si>
   <si>
-    <t>experimental factor 1</t>
+    <t>experimental_factor_1</t>
   </si>
   <si>
     <t>(Optional) A variable that the experiment is based on.</t>
   </si>
   <si>
-    <t>experimental factor 2</t>
-  </si>
-  <si>
-    <t>experimental factor 3</t>
-  </si>
-  <si>
-    <t>experimental factor 4</t>
-  </si>
-  <si>
-    <t>experimental factor 5</t>
+    <t>experimental_factor_2</t>
+  </si>
+  <si>
+    <t>experimental_factor_3</t>
+  </si>
+  <si>
+    <t>experimental_factor_4</t>
+  </si>
+  <si>
+    <t>experimental_factor_5</t>
   </si>
   <si>
     <t>(Optional) A block or batch is an experimental unit arrangement into a group which is similar to one another. typically, a blocking factor is a source of variability that is not of primary interest to the experimenter. an example of a blocking factor might be the sex of a patient; by blocking on sex, this source of variability is controlled for, thus leading to greater accuracy (efo_0005067).</t>
@@ -1928,7 +1961,7 @@
     <t>(Recommended) Name or code for genotype of organism</t>
   </si>
   <si>
-    <t>genetic modification</t>
+    <t>genetic_modification</t>
   </si>
   <si>
     <t>(Optional) A genetic modification of the genome of an organism which may occur naturally by spontaneous mutation, or be introduced by some experimental means. examples of genetic modification include specification of a transgene or the gene knocked-out or details of transient transfection.</t>
@@ -1937,10 +1970,19 @@
     <t>(Optional) The laboratory method used to reveal the presence of the sample sequenced in the experiment.</t>
   </si>
   <si>
+    <t>environmental_stress</t>
+  </si>
+  <si>
     <t>(Optional) Environmental stress is a treatment where some aspect of the environment is perturbed in order to stress the organism or culture, e.g. change in temperature, change in watering regime.</t>
   </si>
   <si>
+    <t>environmental_history</t>
+  </si>
+  <si>
     <t>(Optional) Information concerning the envinonrment a material entity has been exposed to, such as an organism from a lake.</t>
+  </si>
+  <si>
+    <t>growth_condition</t>
   </si>
   <si>
     <t>(Optional) A role that a material entity can play which enables particular conditions used to grow organisms or parts of the organism. this includes isolated environments such as cultures and open environments such as field studies.</t>
@@ -2473,7 +2515,7 @@
         <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2517,7 +2559,7 @@
         <v>144</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2544,7 +2586,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N86"/>
+  <dimension ref="G1:N87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3268,6 +3310,11 @@
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3289,27 +3336,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3329,122 +3376,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3468,240 +3515,240 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>624</v>
+        <v>635</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>625</v>
+        <v>636</v>
       </c>
       <c r="AF1" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="AK1" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="AG1" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>616</v>
-      </c>
       <c r="AL1" s="1" t="s">
-        <v>611</v>
+        <v>644</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>610</v>
+        <v>646</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>613</v>
+        <v>648</v>
       </c>
     </row>
     <row r="2" spans="1:40" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>631</v>
+        <v>642</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>634</v>
+        <v>647</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>635</v>
+        <v>649</v>
       </c>
     </row>
   </sheetData>
@@ -3731,1977 +3778,2002 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="O1:AG289"/>
+  <dimension ref="O1:AG294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="15:33">
       <c r="O1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AC1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="AD1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="AE1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="AF1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="AG1" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
     </row>
     <row r="2" spans="15:33">
       <c r="O2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AC2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AD2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AE2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AF2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="15:33">
       <c r="O3" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AC3" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="AD3" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="AE3" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="AF3" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="AG3" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
     </row>
     <row r="4" spans="15:33">
       <c r="O4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AC4" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="AD4" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="AE4" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="AF4" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="AG4" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
     </row>
     <row r="5" spans="15:33">
       <c r="O5" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AC5" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="AD5" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="AE5" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="AF5" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="AG5" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
     </row>
     <row r="6" spans="15:33">
       <c r="O6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AC6" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="AD6" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="AE6" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="AF6" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="AG6" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
     </row>
     <row r="7" spans="15:33">
       <c r="O7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AC7" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="AD7" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="AE7" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="AF7" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="AG7" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8" spans="15:33">
       <c r="O8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AC8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AD8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AE8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AF8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="15:33">
       <c r="O9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AC9" t="s">
-        <v>586</v>
+        <v>617</v>
       </c>
       <c r="AD9" t="s">
-        <v>586</v>
+        <v>617</v>
       </c>
       <c r="AE9" t="s">
-        <v>586</v>
+        <v>617</v>
       </c>
       <c r="AF9" t="s">
-        <v>586</v>
+        <v>617</v>
       </c>
       <c r="AG9" t="s">
-        <v>586</v>
+        <v>617</v>
       </c>
     </row>
     <row r="10" spans="15:33">
       <c r="O10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AC10" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="AD10" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="AE10" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="AF10" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="AG10" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
     </row>
     <row r="11" spans="15:33">
       <c r="O11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AC11" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="AD11" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="AE11" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="AF11" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="AG11" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="12" spans="15:33">
       <c r="O12" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AC12" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="AD12" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="AE12" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="AF12" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="AG12" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
     </row>
     <row r="13" spans="15:33">
       <c r="O13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AC13" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="AD13" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="AE13" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="AF13" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="AG13" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
     </row>
     <row r="14" spans="15:33">
       <c r="O14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AC14" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="AD14" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="AE14" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="AF14" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="AG14" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
     </row>
     <row r="15" spans="15:33">
       <c r="O15" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AC15" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="AD15" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="AE15" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="AF15" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="AG15" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
     </row>
     <row r="16" spans="15:33">
       <c r="O16" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AC16" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="AD16" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="AE16" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="AF16" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="AG16" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
     </row>
     <row r="17" spans="15:33">
       <c r="O17" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AC17" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="AD17" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="AE17" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="AF17" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="AG17" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
     </row>
     <row r="18" spans="15:33">
       <c r="O18" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AC18" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AD18" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AE18" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AF18" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG18" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="15:33">
       <c r="O19" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AC19" t="s">
-        <v>283</v>
+        <v>622</v>
       </c>
       <c r="AD19" t="s">
-        <v>283</v>
+        <v>622</v>
       </c>
       <c r="AE19" t="s">
-        <v>283</v>
+        <v>622</v>
       </c>
       <c r="AF19" t="s">
-        <v>283</v>
+        <v>622</v>
       </c>
       <c r="AG19" t="s">
-        <v>283</v>
+        <v>622</v>
       </c>
     </row>
     <row r="20" spans="15:33">
       <c r="O20" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AC20" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="AD20" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="AE20" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="AF20" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="AG20" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
     </row>
     <row r="21" spans="15:33">
       <c r="O21" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AC21" t="s">
-        <v>273</v>
+        <v>624</v>
       </c>
       <c r="AD21" t="s">
-        <v>273</v>
+        <v>624</v>
       </c>
       <c r="AE21" t="s">
-        <v>273</v>
+        <v>624</v>
       </c>
       <c r="AF21" t="s">
-        <v>273</v>
+        <v>624</v>
       </c>
       <c r="AG21" t="s">
-        <v>273</v>
+        <v>624</v>
       </c>
     </row>
     <row r="22" spans="15:33">
       <c r="O22" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AC22" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="AD22" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="AE22" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="AF22" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="AG22" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
     </row>
     <row r="23" spans="15:33">
       <c r="O23" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AC23" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AD23" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AE23" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AF23" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG23" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="24" spans="15:33">
       <c r="O24" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AC24" t="s">
-        <v>615</v>
+        <v>625</v>
       </c>
       <c r="AD24" t="s">
-        <v>615</v>
+        <v>625</v>
       </c>
       <c r="AE24" t="s">
-        <v>615</v>
+        <v>625</v>
       </c>
       <c r="AF24" t="s">
-        <v>615</v>
+        <v>625</v>
       </c>
       <c r="AG24" t="s">
-        <v>615</v>
+        <v>625</v>
       </c>
     </row>
     <row r="25" spans="15:33">
       <c r="O25" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AC25" t="s">
-        <v>616</v>
+        <v>626</v>
       </c>
       <c r="AD25" t="s">
-        <v>616</v>
+        <v>626</v>
       </c>
       <c r="AE25" t="s">
-        <v>616</v>
+        <v>626</v>
       </c>
       <c r="AF25" t="s">
-        <v>616</v>
+        <v>626</v>
       </c>
       <c r="AG25" t="s">
-        <v>616</v>
+        <v>626</v>
       </c>
     </row>
     <row r="26" spans="15:33">
       <c r="O26" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AC26" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="AD26" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="AE26" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="AF26" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="AG26" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
     </row>
     <row r="27" spans="15:33">
       <c r="O27" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AC27" t="s">
-        <v>617</v>
+        <v>627</v>
       </c>
       <c r="AD27" t="s">
-        <v>617</v>
+        <v>627</v>
       </c>
       <c r="AE27" t="s">
-        <v>617</v>
+        <v>627</v>
       </c>
       <c r="AF27" t="s">
-        <v>617</v>
+        <v>627</v>
       </c>
       <c r="AG27" t="s">
-        <v>617</v>
+        <v>627</v>
       </c>
     </row>
     <row r="28" spans="15:33">
       <c r="O28" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AC28" t="s">
-        <v>618</v>
+        <v>628</v>
       </c>
       <c r="AD28" t="s">
-        <v>618</v>
+        <v>628</v>
       </c>
       <c r="AE28" t="s">
-        <v>618</v>
+        <v>628</v>
       </c>
       <c r="AF28" t="s">
-        <v>618</v>
+        <v>628</v>
       </c>
       <c r="AG28" t="s">
-        <v>618</v>
+        <v>628</v>
       </c>
     </row>
     <row r="29" spans="15:33">
       <c r="O29" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AC29" t="s">
-        <v>619</v>
+        <v>629</v>
       </c>
       <c r="AD29" t="s">
-        <v>619</v>
+        <v>629</v>
       </c>
       <c r="AE29" t="s">
-        <v>619</v>
+        <v>629</v>
       </c>
       <c r="AF29" t="s">
-        <v>619</v>
+        <v>629</v>
       </c>
       <c r="AG29" t="s">
-        <v>619</v>
+        <v>629</v>
       </c>
     </row>
     <row r="30" spans="15:33">
       <c r="O30" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AC30" t="s">
-        <v>281</v>
+        <v>630</v>
       </c>
       <c r="AD30" t="s">
-        <v>281</v>
+        <v>630</v>
       </c>
       <c r="AE30" t="s">
-        <v>281</v>
+        <v>630</v>
       </c>
       <c r="AF30" t="s">
-        <v>281</v>
+        <v>630</v>
       </c>
       <c r="AG30" t="s">
-        <v>281</v>
+        <v>630</v>
       </c>
     </row>
     <row r="31" spans="15:33">
       <c r="O31" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AC31" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AD31" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AE31" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AF31" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG31" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="32" spans="15:33">
       <c r="O32" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AC32" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="AD32" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="AE32" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="AF32" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="AG32" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
     </row>
     <row r="33" spans="15:33">
       <c r="O33" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AC33" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="AD33" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="AE33" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="AF33" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="AG33" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
     </row>
     <row r="34" spans="15:33">
       <c r="O34" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AC34" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="AD34" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="AE34" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="AF34" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="AG34" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
     </row>
     <row r="35" spans="15:33">
       <c r="O35" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AC35" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c r="AD35" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c r="AE35" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c r="AF35" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c r="AG35" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
     </row>
     <row r="36" spans="15:33">
       <c r="O36" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="37" spans="15:33">
       <c r="O37" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="38" spans="15:33">
       <c r="O38" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="39" spans="15:33">
       <c r="O39" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="40" spans="15:33">
       <c r="O40" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="41" spans="15:33">
       <c r="O41" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="42" spans="15:33">
       <c r="O42" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="43" spans="15:33">
       <c r="O43" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="44" spans="15:33">
       <c r="O44" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="45" spans="15:33">
       <c r="O45" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="46" spans="15:33">
       <c r="O46" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="47" spans="15:33">
       <c r="O47" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="48" spans="15:33">
       <c r="O48" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="49" spans="15:15">
       <c r="O49" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="50" spans="15:15">
       <c r="O50" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="51" spans="15:15">
       <c r="O51" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="52" spans="15:15">
       <c r="O52" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="53" spans="15:15">
       <c r="O53" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="54" spans="15:15">
       <c r="O54" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="55" spans="15:15">
       <c r="O55" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="56" spans="15:15">
       <c r="O56" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="57" spans="15:15">
       <c r="O57" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="58" spans="15:15">
       <c r="O58" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="59" spans="15:15">
       <c r="O59" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="60" spans="15:15">
       <c r="O60" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="61" spans="15:15">
       <c r="O61" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="62" spans="15:15">
       <c r="O62" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="63" spans="15:15">
       <c r="O63" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="64" spans="15:15">
       <c r="O64" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="65" spans="15:15">
       <c r="O65" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="66" spans="15:15">
       <c r="O66" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="67" spans="15:15">
       <c r="O67" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="68" spans="15:15">
       <c r="O68" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="69" spans="15:15">
       <c r="O69" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="70" spans="15:15">
       <c r="O70" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="71" spans="15:15">
       <c r="O71" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="72" spans="15:15">
       <c r="O72" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="73" spans="15:15">
       <c r="O73" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="74" spans="15:15">
       <c r="O74" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="75" spans="15:15">
       <c r="O75" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="76" spans="15:15">
       <c r="O76" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="77" spans="15:15">
       <c r="O77" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="78" spans="15:15">
       <c r="O78" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="79" spans="15:15">
       <c r="O79" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="80" spans="15:15">
       <c r="O80" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="81" spans="15:15">
       <c r="O81" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="82" spans="15:15">
       <c r="O82" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="83" spans="15:15">
       <c r="O83" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="84" spans="15:15">
       <c r="O84" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="85" spans="15:15">
       <c r="O85" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="86" spans="15:15">
       <c r="O86" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="87" spans="15:15">
       <c r="O87" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="88" spans="15:15">
       <c r="O88" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="89" spans="15:15">
       <c r="O89" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="90" spans="15:15">
       <c r="O90" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="91" spans="15:15">
       <c r="O91" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="92" spans="15:15">
       <c r="O92" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="93" spans="15:15">
       <c r="O93" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="94" spans="15:15">
       <c r="O94" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="95" spans="15:15">
       <c r="O95" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="96" spans="15:15">
       <c r="O96" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="97" spans="15:15">
       <c r="O97" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="98" spans="15:15">
       <c r="O98" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="99" spans="15:15">
       <c r="O99" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="100" spans="15:15">
       <c r="O100" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="101" spans="15:15">
       <c r="O101" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="102" spans="15:15">
       <c r="O102" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="103" spans="15:15">
       <c r="O103" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="104" spans="15:15">
       <c r="O104" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="105" spans="15:15">
       <c r="O105" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="106" spans="15:15">
       <c r="O106" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="107" spans="15:15">
       <c r="O107" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="108" spans="15:15">
       <c r="O108" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="109" spans="15:15">
       <c r="O109" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="110" spans="15:15">
       <c r="O110" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="111" spans="15:15">
       <c r="O111" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="112" spans="15:15">
       <c r="O112" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="113" spans="15:15">
       <c r="O113" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="114" spans="15:15">
       <c r="O114" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="115" spans="15:15">
       <c r="O115" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="116" spans="15:15">
       <c r="O116" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="117" spans="15:15">
       <c r="O117" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="118" spans="15:15">
       <c r="O118" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="119" spans="15:15">
       <c r="O119" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="120" spans="15:15">
       <c r="O120" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="121" spans="15:15">
       <c r="O121" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="122" spans="15:15">
       <c r="O122" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="123" spans="15:15">
       <c r="O123" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="124" spans="15:15">
       <c r="O124" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="125" spans="15:15">
       <c r="O125" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="126" spans="15:15">
       <c r="O126" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="127" spans="15:15">
       <c r="O127" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="128" spans="15:15">
       <c r="O128" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="129" spans="15:15">
       <c r="O129" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="130" spans="15:15">
       <c r="O130" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="131" spans="15:15">
       <c r="O131" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="132" spans="15:15">
       <c r="O132" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="133" spans="15:15">
       <c r="O133" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="134" spans="15:15">
       <c r="O134" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="135" spans="15:15">
       <c r="O135" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="136" spans="15:15">
       <c r="O136" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="137" spans="15:15">
       <c r="O137" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="138" spans="15:15">
       <c r="O138" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="139" spans="15:15">
       <c r="O139" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="140" spans="15:15">
       <c r="O140" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="141" spans="15:15">
       <c r="O141" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="142" spans="15:15">
       <c r="O142" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="143" spans="15:15">
       <c r="O143" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="144" spans="15:15">
       <c r="O144" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="145" spans="15:15">
       <c r="O145" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="146" spans="15:15">
       <c r="O146" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="147" spans="15:15">
       <c r="O147" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="148" spans="15:15">
       <c r="O148" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="149" spans="15:15">
       <c r="O149" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="150" spans="15:15">
       <c r="O150" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="151" spans="15:15">
       <c r="O151" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="152" spans="15:15">
       <c r="O152" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="153" spans="15:15">
       <c r="O153" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="154" spans="15:15">
       <c r="O154" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="155" spans="15:15">
       <c r="O155" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="156" spans="15:15">
       <c r="O156" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="157" spans="15:15">
       <c r="O157" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="158" spans="15:15">
       <c r="O158" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="159" spans="15:15">
       <c r="O159" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="160" spans="15:15">
       <c r="O160" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="161" spans="15:15">
       <c r="O161" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="162" spans="15:15">
       <c r="O162" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="163" spans="15:15">
       <c r="O163" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="164" spans="15:15">
       <c r="O164" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="165" spans="15:15">
       <c r="O165" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="166" spans="15:15">
       <c r="O166" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="167" spans="15:15">
       <c r="O167" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="168" spans="15:15">
       <c r="O168" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="169" spans="15:15">
       <c r="O169" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="170" spans="15:15">
       <c r="O170" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="171" spans="15:15">
       <c r="O171" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="172" spans="15:15">
       <c r="O172" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="173" spans="15:15">
       <c r="O173" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="174" spans="15:15">
       <c r="O174" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="175" spans="15:15">
       <c r="O175" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="176" spans="15:15">
       <c r="O176" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="177" spans="15:15">
       <c r="O177" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="178" spans="15:15">
       <c r="O178" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="179" spans="15:15">
       <c r="O179" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="180" spans="15:15">
       <c r="O180" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="181" spans="15:15">
       <c r="O181" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="182" spans="15:15">
       <c r="O182" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="183" spans="15:15">
       <c r="O183" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="184" spans="15:15">
       <c r="O184" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="185" spans="15:15">
       <c r="O185" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="186" spans="15:15">
       <c r="O186" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="187" spans="15:15">
       <c r="O187" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="188" spans="15:15">
       <c r="O188" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="189" spans="15:15">
       <c r="O189" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="190" spans="15:15">
       <c r="O190" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="191" spans="15:15">
       <c r="O191" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="192" spans="15:15">
       <c r="O192" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="193" spans="15:15">
       <c r="O193" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="194" spans="15:15">
       <c r="O194" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="195" spans="15:15">
       <c r="O195" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="196" spans="15:15">
       <c r="O196" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="197" spans="15:15">
       <c r="O197" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="198" spans="15:15">
       <c r="O198" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="199" spans="15:15">
       <c r="O199" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="200" spans="15:15">
       <c r="O200" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="201" spans="15:15">
       <c r="O201" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="202" spans="15:15">
       <c r="O202" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="203" spans="15:15">
       <c r="O203" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="204" spans="15:15">
       <c r="O204" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="205" spans="15:15">
       <c r="O205" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="206" spans="15:15">
       <c r="O206" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="207" spans="15:15">
       <c r="O207" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="208" spans="15:15">
       <c r="O208" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="209" spans="15:15">
       <c r="O209" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="210" spans="15:15">
       <c r="O210" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="211" spans="15:15">
       <c r="O211" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="212" spans="15:15">
       <c r="O212" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="213" spans="15:15">
       <c r="O213" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="214" spans="15:15">
       <c r="O214" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="215" spans="15:15">
       <c r="O215" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="216" spans="15:15">
       <c r="O216" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="217" spans="15:15">
       <c r="O217" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="218" spans="15:15">
       <c r="O218" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="219" spans="15:15">
       <c r="O219" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="220" spans="15:15">
       <c r="O220" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="221" spans="15:15">
       <c r="O221" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="222" spans="15:15">
       <c r="O222" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="223" spans="15:15">
       <c r="O223" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="224" spans="15:15">
       <c r="O224" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="225" spans="15:15">
       <c r="O225" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="226" spans="15:15">
       <c r="O226" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="227" spans="15:15">
       <c r="O227" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="228" spans="15:15">
       <c r="O228" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="229" spans="15:15">
       <c r="O229" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="230" spans="15:15">
       <c r="O230" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="231" spans="15:15">
       <c r="O231" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="232" spans="15:15">
       <c r="O232" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="233" spans="15:15">
       <c r="O233" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="234" spans="15:15">
       <c r="O234" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="235" spans="15:15">
       <c r="O235" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="236" spans="15:15">
       <c r="O236" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="237" spans="15:15">
       <c r="O237" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="238" spans="15:15">
       <c r="O238" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="239" spans="15:15">
       <c r="O239" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="240" spans="15:15">
       <c r="O240" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="241" spans="15:15">
       <c r="O241" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="242" spans="15:15">
       <c r="O242" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="243" spans="15:15">
       <c r="O243" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="244" spans="15:15">
       <c r="O244" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="245" spans="15:15">
       <c r="O245" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="246" spans="15:15">
       <c r="O246" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="247" spans="15:15">
       <c r="O247" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="248" spans="15:15">
       <c r="O248" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="249" spans="15:15">
       <c r="O249" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="250" spans="15:15">
       <c r="O250" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="251" spans="15:15">
       <c r="O251" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="252" spans="15:15">
       <c r="O252" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="253" spans="15:15">
       <c r="O253" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="254" spans="15:15">
       <c r="O254" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="255" spans="15:15">
       <c r="O255" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="256" spans="15:15">
       <c r="O256" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="257" spans="15:15">
       <c r="O257" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="258" spans="15:15">
       <c r="O258" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="259" spans="15:15">
       <c r="O259" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="260" spans="15:15">
       <c r="O260" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="261" spans="15:15">
       <c r="O261" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="262" spans="15:15">
       <c r="O262" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="263" spans="15:15">
       <c r="O263" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="264" spans="15:15">
       <c r="O264" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="265" spans="15:15">
       <c r="O265" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="266" spans="15:15">
       <c r="O266" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="267" spans="15:15">
       <c r="O267" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="268" spans="15:15">
       <c r="O268" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="269" spans="15:15">
       <c r="O269" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="270" spans="15:15">
       <c r="O270" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="271" spans="15:15">
       <c r="O271" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="272" spans="15:15">
       <c r="O272" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="273" spans="15:15">
       <c r="O273" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="274" spans="15:15">
       <c r="O274" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="275" spans="15:15">
       <c r="O275" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="276" spans="15:15">
       <c r="O276" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="277" spans="15:15">
       <c r="O277" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="278" spans="15:15">
       <c r="O278" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="279" spans="15:15">
       <c r="O279" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="280" spans="15:15">
       <c r="O280" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="281" spans="15:15">
       <c r="O281" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="282" spans="15:15">
       <c r="O282" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="283" spans="15:15">
       <c r="O283" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="284" spans="15:15">
       <c r="O284" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="285" spans="15:15">
       <c r="O285" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="286" spans="15:15">
       <c r="O286" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="287" spans="15:15">
       <c r="O287" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="288" spans="15:15">
       <c r="O288" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="289" spans="15:15">
       <c r="O289" t="s">
-        <v>577</v>
+        <v>578</v>
+      </c>
+    </row>
+    <row r="290" spans="15:15">
+      <c r="O290" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="291" spans="15:15">
+      <c r="O291" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="292" spans="15:15">
+      <c r="O292" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="293" spans="15:15">
+      <c r="O293" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="294" spans="15:15">
+      <c r="O294" t="s">
+        <v>583</v>
       </c>
     </row>
   </sheetData>
